--- a/sample_data/wedstrijd-data-2026-08-15.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-15.xlsx
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>271.337833</v>
+        <v>210.367</v>
       </c>
       <c r="D6" t="n">
-        <v>248.317888</v>
+        <v>273.277158</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>233.218394</v>
+        <v>223.958238</v>
       </c>
       <c r="D8" t="n">
-        <v>286.188359</v>
+        <v>294.688515</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>330.172637</v>
+        <v>337.643802</v>
       </c>
       <c r="D16" t="n">
-        <v>280.029983</v>
+        <v>284.811458</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>258.609947</v>
+        <v>206.113025</v>
       </c>
       <c r="D17" t="n">
-        <v>242.728362</v>
+        <v>233.389022</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>271.96255</v>
+        <v>246.078577</v>
       </c>
       <c r="D20" t="n">
-        <v>256.592827</v>
+        <v>311.022039</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>334.574717</v>
+        <v>344.699329</v>
       </c>
       <c r="D32" t="n">
-        <v>266.845519</v>
+        <v>270.511239</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>323.700373</v>
+        <v>326.880825</v>
       </c>
       <c r="D34" t="n">
-        <v>294.611484</v>
+        <v>297.922089</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-08-15.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-15.xlsx
@@ -1078,10 +1078,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>238.996376</v>
+        <v>268.496824</v>
       </c>
       <c r="D2" t="n">
-        <v>110.414541</v>
+        <v>124.273157</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>100.181751</v>
+        <v>112.547656</v>
       </c>
       <c r="D3" t="n">
-        <v>318.081937</v>
+        <v>358.005801</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>392.911228</v>
+        <v>441.410109</v>
       </c>
       <c r="D4" t="n">
-        <v>330.446812</v>
+        <v>371.922647</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>181.093802</v>
+        <v>203.447062</v>
       </c>
       <c r="D5" t="n">
-        <v>264.519976</v>
+        <v>297.721043</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>210.367</v>
+        <v>236.333589</v>
       </c>
       <c r="D6" t="n">
-        <v>273.277158</v>
+        <v>307.577377</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>294.805899</v>
+        <v>331.195178</v>
       </c>
       <c r="D7" t="n">
-        <v>320.970559</v>
+        <v>361.256987</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>223.958238</v>
+        <v>251.602457</v>
       </c>
       <c r="D8" t="n">
-        <v>294.688515</v>
+        <v>331.676168</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>341.992304</v>
+        <v>384.206023</v>
       </c>
       <c r="D9" t="n">
-        <v>187.775154</v>
+        <v>211.34364</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>96.08103699999999</v>
+        <v>107.940772</v>
       </c>
       <c r="D10" t="n">
-        <v>237.597013</v>
+        <v>267.41886</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>438.910057</v>
+        <v>493.08679</v>
       </c>
       <c r="D11" t="n">
-        <v>191.664033</v>
+        <v>215.72063</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>412.45147</v>
+        <v>463.362295</v>
       </c>
       <c r="D12" t="n">
-        <v>218.791118</v>
+        <v>246.252555</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>236.025245</v>
+        <v>265.158951</v>
       </c>
       <c r="D13" t="n">
-        <v>133.387724</v>
+        <v>150.129805</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>260.299388</v>
+        <v>292.429366</v>
       </c>
       <c r="D14" t="n">
-        <v>157.806637</v>
+        <v>177.613642</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>426.924872</v>
+        <v>479.622218</v>
       </c>
       <c r="D15" t="n">
-        <v>148.599441</v>
+        <v>167.250811</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>337.643802</v>
+        <v>379.320765</v>
       </c>
       <c r="D16" t="n">
-        <v>284.811458</v>
+        <v>320.559398</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>206.113025</v>
+        <v>231.554525</v>
       </c>
       <c r="D17" t="n">
-        <v>233.389022</v>
+        <v>262.682706</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>184.180409</v>
+        <v>206.914664</v>
       </c>
       <c r="D18" t="n">
-        <v>191.930977</v>
+        <v>216.02108</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>181.156902</v>
+        <v>203.51795</v>
       </c>
       <c r="D19" t="n">
-        <v>172.256607</v>
+        <v>193.877293</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>246.078577</v>
+        <v>276.453213</v>
       </c>
       <c r="D20" t="n">
-        <v>311.022039</v>
+        <v>350.059785</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>479.607766</v>
+        <v>538.808009</v>
       </c>
       <c r="D21" t="n">
-        <v>237.187002</v>
+        <v>266.957387</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>107.356811</v>
+        <v>120.608367</v>
       </c>
       <c r="D22" t="n">
-        <v>320.662468</v>
+        <v>360.910226</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>436.533736</v>
+        <v>490.417149</v>
       </c>
       <c r="D23" t="n">
-        <v>234.762554</v>
+        <v>264.228636</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>141.513807</v>
+        <v>158.981521</v>
       </c>
       <c r="D24" t="n">
-        <v>183.627593</v>
+        <v>206.6755</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>286.084669</v>
+        <v>321.397446</v>
       </c>
       <c r="D25" t="n">
-        <v>132.428484</v>
+        <v>149.050167</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>287.565024</v>
+        <v>323.060528</v>
       </c>
       <c r="D26" t="n">
-        <v>156.329109</v>
+        <v>175.950664</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>237.268408</v>
+        <v>266.555564</v>
       </c>
       <c r="D27" t="n">
-        <v>115.522606</v>
+        <v>130.022357</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>435.446443</v>
+        <v>489.195646</v>
       </c>
       <c r="D28" t="n">
-        <v>131.547663</v>
+        <v>148.05879</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>443.483359</v>
+        <v>498.224596</v>
       </c>
       <c r="D29" t="n">
-        <v>192.695607</v>
+        <v>216.881682</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>263.650231</v>
+        <v>296.193819</v>
       </c>
       <c r="D30" t="n">
-        <v>121.15618</v>
+        <v>136.363026</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>460.026312</v>
+        <v>516.809524</v>
       </c>
       <c r="D31" t="n">
-        <v>247.608274</v>
+        <v>278.686679</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>344.699329</v>
+        <v>387.247189</v>
       </c>
       <c r="D32" t="n">
-        <v>270.511239</v>
+        <v>304.464295</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>344.95329</v>
+        <v>387.532497</v>
       </c>
       <c r="D33" t="n">
-        <v>182.790069</v>
+        <v>205.732855</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>326.880825</v>
+        <v>367.229263</v>
       </c>
       <c r="D34" t="n">
-        <v>297.922089</v>
+        <v>335.315602</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>92.072592</v>
+        <v>103.437546</v>
       </c>
       <c r="D35" t="n">
-        <v>129.23436</v>
+        <v>145.455133</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>397.752187</v>
+        <v>446.84861</v>
       </c>
       <c r="D36" t="n">
-        <v>179.352222</v>
+        <v>201.86351</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>409.248157</v>
+        <v>459.763582</v>
       </c>
       <c r="D37" t="n">
-        <v>224.066003</v>
+        <v>252.189514</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>344.467815</v>
+        <v>386.987098</v>
       </c>
       <c r="D38" t="n">
-        <v>186.106882</v>
+        <v>209.465976</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
